--- a/data/trans_orig/IP25B02_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22295</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35154</t>
+          <t>36791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53056</t>
+          <t>52830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>19911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>35430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26217</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>45769</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>51586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75934</t>
+          <t>75696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36221</t>
+          <t>36726</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>31727</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54953</t>
+          <t>54169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55274</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83864</t>
+          <t>85584</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24678</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39469</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>28397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47565</t>
+          <t>48544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56630</t>
+          <t>58677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82566</t>
+          <t>82337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>20418</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>25508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23653</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29353</t>
+          <t>29866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37227</t>
+          <t>37188</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61135</t>
+          <t>62124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34254</t>
+          <t>33932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37108</t>
+          <t>37957</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45455</t>
+          <t>44802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>66390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22620</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37502</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40237</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59816</t>
+          <t>59889</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>41910</t>
+          <t>43380</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40743</t>
+          <t>40863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23419</t>
+          <t>23299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44687</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111092</t>
+          <t>109188</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40913</t>
+          <t>41054</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72777</t>
+          <t>71694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73325</t>
+          <t>73390</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169223</t>
+          <t>176470</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32855</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>65646</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>32129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53843</t>
+          <t>54903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74416</t>
+          <t>74189</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111671</t>
+          <t>113115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71141</t>
+          <t>69226</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50064</t>
+          <t>51136</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78235</t>
+          <t>76821</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>92143</t>
+          <t>92177</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>139880</t>
+          <t>137031</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39551</t>
+          <t>39520</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80280</t>
+          <t>79327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44666</t>
+          <t>44554</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68344</t>
+          <t>67473</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94761</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139032</t>
+          <t>141290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28320</t>
+          <t>27877</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25296</t>
+          <t>25227</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>67335</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43790</t>
+          <t>42116</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87018</t>
+          <t>85535</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>27194</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46447</t>
+          <t>45486</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30902</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54057</t>
+          <t>55036</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63466</t>
+          <t>65620</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94076</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38479</t>
+          <t>38348</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33622</t>
+          <t>32494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>55934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62418</t>
+          <t>60103</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>89452</t>
+          <t>89397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38132</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>24360</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>44516</t>
+          <t>44373</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>52312</t>
+          <t>52082</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>76380</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>17272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21748</t>
+          <t>20919</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31449</t>
+          <t>33057</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30900</t>
+          <t>30923</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>49797</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26272</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31457</t>
+          <t>31442</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>49623</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>28967</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>10764</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>48262</t>
+          <t>47319</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>84993</t>
+          <t>83736</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>202841</t>
+          <t>196977</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>124826</t>
+          <t>123565</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>181477</t>
+          <t>182107</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>224277</t>
+          <t>221624</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>345469</t>
+          <t>350993</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>136620</t>
+          <t>139646</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>186006</t>
+          <t>188239</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>173591</t>
+          <t>173225</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>218108</t>
+          <t>220082</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>322777</t>
+          <t>324579</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>391432</t>
+          <t>394676</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>143631</t>
+          <t>145082</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>194907</t>
+          <t>195932</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>190463</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>240268</t>
+          <t>240605</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>355308</t>
+          <t>354886</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>423061</t>
+          <t>422014</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>161504</t>
+          <t>164010</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>215851</t>
+          <t>214328</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>161861</t>
+          <t>160549</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>202944</t>
+          <t>205783</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>338934</t>
+          <t>337759</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>403865</t>
+          <t>405767</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B02_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos en fines de semana / solo 2023 en 2023 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos en fin de semana en 2023 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13685</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8540</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21208</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15637</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10209</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23316</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36791</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35276</t>
+          <t>29987</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52830</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35200</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26089</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>44417</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>27212</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19911</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35430</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26187</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45769</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>62740</t>
+          <t>63453</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51586</t>
+          <t>52470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75696</t>
+          <t>75712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38310</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28955</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47698</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>39,44%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>27145</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20077</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>36726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42072</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31727</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54169</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>69217</t>
+          <t>63536</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>51495</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85584</t>
+          <t>75442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33738</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26551</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43183</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>35,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>31284</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>23922</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39174</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28397</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48544</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>69241</t>
+          <t>63937</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58677</t>
+          <t>53398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82337</t>
+          <t>75885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>120932</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>120932</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>120932</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>135196</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135196</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135196</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>236474</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236474</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236474</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17254</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11629</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>24854</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>27,19%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>13772</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8404</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>20418</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>21108</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>31742</t>
+          <t>31419</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>23706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41917</t>
+          <t>40633</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28070</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20414</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36669</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>22145</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15901</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29866</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37188</t>
+          <t>30414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50837</t>
+          <t>51161</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40622</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62124</t>
+          <t>62434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>21672</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33932</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>26931</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>20355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>34942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>55431</t>
+          <t>55524</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44802</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66390</t>
+          <t>66602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17480</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12071</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23741</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>29863</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22899</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38086</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>32,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>24,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>41,45%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>29776</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>38221</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>49437</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40065</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59889</t>
+          <t>56771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>91874</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>91874</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>91874</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>93962</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>93962</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>93962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>187447</t>
+          <t>185360</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187447</t>
+          <t>185360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187447</t>
+          <t>185360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>22462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20751</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14629</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>49,09%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>11151</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>6753</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>16984</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>21,78%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>32826</t>
+          <t>33001</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13259</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8523</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18972</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17380</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11807</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23377</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14148</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20483</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>31529</t>
+          <t>32516</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>41581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14225</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9543</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20316</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>16813</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11263</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23299</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>32,84%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>35218</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>22170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44369</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>51192</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>51192</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>51192</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>115045</t>
+          <t>109775</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115045</t>
+          <t>109775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115045</t>
+          <t>109775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>52055</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>40577</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>70347</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>20,27%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>47079</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>21209</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>109188</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54517</t>
+          <t>23359</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41054</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>33287</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>101596</t>
+          <t>75414</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73390</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176470</t>
+          <t>94541</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>39906</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30376</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>51748</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>25,85%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>50763</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>33026</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>65646</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>30,6%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>47150</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>38447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54903</t>
+          <t>58310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>93950</t>
+          <t>87057</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74189</t>
+          <t>72837</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113115</t>
+          <t>102269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -2653,107 +2653,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>58400</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>46051</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72405</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>29,17%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>36,17%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>54253</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>35624</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>69226</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>51005</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>40670</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>60969</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>34,78%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>109405</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>94949</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>125712</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>16,61%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>62881</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>51136</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>76821</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>29,07%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>35,51%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>117135</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>92177</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>137031</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>27,19%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>21,39%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>49824</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>39545</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>61191</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>30,57%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>62432</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>39520</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>79327</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>36,98%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>53760</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>43705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67473</t>
+          <t>63903</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>118188</t>
+          <t>103584</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94706</t>
+          <t>88705</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141290</t>
+          <t>118120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>200185</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>200185</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>200185</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>214527</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>214527</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>214527</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>216342</t>
+          <t>175274</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>216342</t>
+          <t>175274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216342</t>
+          <t>175274</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>430869</t>
+          <t>375459</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>430869</t>
+          <t>375459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>430869</t>
+          <t>375459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>34605</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22988</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>55619</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>23,91%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>15,88%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>38,43%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>20110</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>14078</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>27877</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>17,37%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37517</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25227</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67335</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>57627</t>
+          <t>55124</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42116</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85535</t>
+          <t>78656</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>37846</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>28171</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>48862</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>19,46%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>33,76%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>35850</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>27194</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>45486</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>30,97%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>23,49%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>39,29%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>27009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55036</t>
+          <t>45593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>78554</t>
+          <t>73417</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65620</t>
+          <t>61051</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>87604</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>43109</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>32430</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>54511</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>22,41%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>37,66%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>30075</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>22539</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>38348</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>25,98%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>33,13%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>45242</t>
+          <t>30626</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32494</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55934</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>75317</t>
+          <t>73734</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60103</t>
+          <t>61562</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>89397</t>
+          <t>88320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>29185</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>21085</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>38841</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>20,16%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>26,83%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>29723</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>22848</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>37981</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>25,68%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>19,74%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>32,81%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>21704</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>44373</t>
+          <t>36828</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>63407</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>52082</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>78943</t>
+          <t>70257</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>144744</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>144744</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>144744</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>115757</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>115757</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>115757</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>159147</t>
+          <t>115212</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>159147</t>
+          <t>115212</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>159147</t>
+          <t>115212</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>274905</t>
+          <t>259957</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>274905</t>
+          <t>259957</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>274905</t>
+          <t>259957</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,72 +3565,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>8603</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>4378</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>14893</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,95%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>22,41%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>10832</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>6118</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>17272</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27913</t>
+          <t>28657</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -3678,72 +3678,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>24104</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>17430</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>31378</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>36,27%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>47,21%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>15080</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>9686</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>20919</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>31,32%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33057</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30923</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>51792</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -3791,72 +3791,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>20749</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>14353</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>27475</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>19397</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>13190</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>26212</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>39,24%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>27803</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31442</t>
+          <t>31274</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49623</t>
+          <t>51075</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -3904,72 +3904,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>13004</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>8415</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>19012</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>19,57%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>21490</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>15278</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>28967</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>32,17%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>22,87%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>43,37%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>27029</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>37979</t>
+          <t>32640</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29205</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47319</t>
+          <t>40923</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>66799</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>66799</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>66799</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>68416</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>68416</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>68416</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>136951</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>136951</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>136951</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>134907</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>113192</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>166727</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>16,63%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>24,49%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>113276</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>83736</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>196977</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>147757</t>
+          <t>91697</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>123565</t>
+          <t>76137</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>182107</t>
+          <t>108510</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>261034</t>
+          <t>226605</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>221624</t>
+          <t>198701</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>350993</t>
+          <t>260705</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>185877</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>163946</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>207144</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>24,09%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>30,43%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>162201</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>139646</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>188239</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>21,77%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>196075</t>
+          <t>163222</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>173225</t>
+          <t>145448</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>220082</t>
+          <t>182247</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>358276</t>
+          <t>349100</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>324579</t>
+          <t>319784</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>394676</t>
+          <t>377374</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -4360,72 +4360,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>202419</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>180906</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>226805</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>33,32%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>174345</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>145082</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>195932</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>27,18%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>22,62%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>30,55%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>214565</t>
+          <t>173571</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>190463</t>
+          <t>156173</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>240605</t>
+          <t>194221</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>388910</t>
+          <t>375990</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>354886</t>
+          <t>346500</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>422014</t>
+          <t>405587</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>157456</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>138238</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>176151</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>23,13%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>25,88%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>191605</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>164010</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>214328</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>29,87%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>33,41%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>181866</t>
+          <t>177189</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>160549</t>
+          <t>159044</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>205783</t>
+          <t>197017</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>373470</t>
+          <t>334645</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>337759</t>
+          <t>307490</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>405767</t>
+          <t>363174</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>680659</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>680659</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>680659</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>904</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>641427</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>641427</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>641427</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>948</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>740263</t>
+          <t>605680</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>740263</t>
+          <t>605680</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>740263</t>
+          <t>605680</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1381690</t>
+          <t>1286339</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1381690</t>
+          <t>1286339</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1381690</t>
+          <t>1286339</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
